--- a/02_DIA_inicio_2026_analisis_assets/rbd_9410_escuela-consolidada-davila_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9410_escuela-consolidada-davila_nt1_rubricas.xlsx
@@ -1788,13 +1788,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA4942CE-8E07-4174-8D1B-F29E9A494AA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F784031-0C91-4ACB-911F-BA3DF11F4E4A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2155E3-6AC1-44F1-9235-8909431DA511}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABB73DA7-2B4A-40E8-9DB5-8C21B2946668}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1EE0186-06F2-44AE-89D2-7C5A05D8607A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8577B3BC-994E-4CD0-82AA-7362BDDC9356}"/>
 </file>